--- a/BASE/BASE.xlsx
+++ b/BASE/BASE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\NFSROBOT\HALS-Documentation\BASE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\NFSROBOT\HALS-Documentation\GitHub-BASE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4069B9FA-D086-4125-9485-B69FBFBF77CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B88DB8-C05E-472D-A87A-DEAEC38A5D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="345" windowWidth="23760" windowHeight="15000" xr2:uid="{2627D5EB-CB7B-465B-86CB-7522549758FD}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{2627D5EB-CB7B-465B-86CB-7522549758FD}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE; Foot &amp; main axle" sheetId="1" r:id="rId1"/>
@@ -54,9 +54,6 @@
     <t>Base002</t>
   </si>
   <si>
-    <t>For the moment I only use the base tube of the central axis, its diameter is ~41.5mm . The extenstion tube is not used, it is also not very straight.</t>
-  </si>
-  <si>
     <t>Base003</t>
   </si>
   <si>
@@ -67,9 +64,6 @@
   </si>
   <si>
     <t>Base005</t>
-  </si>
-  <si>
-    <t>The central pillar is hollow, and has a 15mm hole close to the top, in order to pass the loudspeaker cable through the hollow pillar near the bottom a hole is needed. ~15mm.  Revised, the loudspeaker cable goes via the Stool into the central pillar, still need a hole in the bottom of the pillar.</t>
   </si>
   <si>
     <t>Base006</t>
@@ -193,9 +187,6 @@
     <t>BASE002</t>
   </si>
   <si>
-    <t>Level adjustment M8x24 screw</t>
-  </si>
-  <si>
     <t>BASE003</t>
   </si>
   <si>
@@ -211,9 +202,6 @@
     <t>Extra Mass ~ 7kg on tripod leg</t>
   </si>
   <si>
-    <t>Essential to preven tipping</t>
-  </si>
-  <si>
     <t>BASE005</t>
   </si>
   <si>
@@ -242,6 +230,31 @@
   </si>
   <si>
     <t>BOM for the HALS-Mechatronics BASE</t>
+  </si>
+  <si>
+    <t>For the moment I only use the base tube of the central axis, its diameter is ~41.3mm . The extenstion tube is not used, it is also not very straight.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The central pillar is hollow, and has a 15mm hole close to the top, in order to pass the loudspeaker cable through the hollow pillar near the bottom a hole is needed. ~15mm.  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Revised, the loudspeaker cable goes via the Stool into the central pillar, still need a hole in the bottom of the pillar.</t>
+    </r>
+  </si>
+  <si>
+    <t>Level adjustment M8x24 foot/screw</t>
+  </si>
+  <si>
+    <t>Essential to prevent tipping, a tile or a self-made concrete mass see 3D model</t>
   </si>
 </sst>
 </file>
@@ -432,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -447,9 +460,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -458,12 +468,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -474,6 +478,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1018,18 +1025,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
-        <v>23</v>
+      <c r="B1" s="16" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="15" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1038,90 +1045,90 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="3" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B13" s="3"/>
     </row>
     <row r="18" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1139,225 +1146,225 @@
   <cols>
     <col min="3" max="3" width="43.85546875" customWidth="1"/>
     <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="61.42578125" customWidth="1"/>
+    <col min="6" max="6" width="69.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="13"/>
+    </row>
+    <row r="3" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="7">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="6">
+        <v>3</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="6">
+        <v>3</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="6">
+        <v>3</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="6">
+        <v>3</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="14"/>
-    </row>
-    <row r="3" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="10" t="s">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="8" t="s">
+      <c r="B9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="6">
+        <v>3</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="6">
+        <v>3</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="8">
-        <v>1</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="7">
-        <v>3</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="7">
-        <v>3</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="7">
-        <v>3</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="7">
-        <v>3</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="7">
-        <v>3</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="7">
-        <v>3</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>48</v>
-      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:F16" xr:uid="{D99DBC6D-CD22-4065-BC1A-0B9DFEE9E78B}"/>

--- a/BASE/BASE.xlsx
+++ b/BASE/BASE.xlsx
@@ -1,46 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\NFSROBOT\HALS-Documentation\GitHub-BASE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HALS-DOCUMENTATION\GitHub-BASE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B88DB8-C05E-472D-A87A-DEAEC38A5D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F3952BC-A669-45DB-98A2-0AB172487019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{2627D5EB-CB7B-465B-86CB-7522549758FD}"/>
+    <workbookView xWindow="29580" yWindow="780" windowWidth="16365" windowHeight="11295" activeTab="1" xr2:uid="{2627D5EB-CB7B-465B-86CB-7522549758FD}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE; Foot &amp; main axle" sheetId="1" r:id="rId1"/>
     <sheet name="BASE; BOM" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BASE; BOM'!$A$3:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BASE; BOM'!$A$3:$F$17</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="56">
   <si>
     <t>#</t>
   </si>
@@ -255,6 +244,12 @@
   </si>
   <si>
     <t>Essential to prevent tipping, a tile or a self-made concrete mass see 3D model</t>
+  </si>
+  <si>
+    <t>BASE008</t>
+  </si>
+  <si>
+    <t>Extra Mass ~ 7kg casting mould, 2 parts</t>
   </si>
 </sst>
 </file>
@@ -1141,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EE8B0D7-CF69-4473-81FF-19193248B78E}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="43.85546875" customWidth="1"/>
@@ -1266,16 +1261,16 @@
         <v>40</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D8" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1286,16 +1281,16 @@
         <v>42</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D9" s="6">
         <v>3</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1306,25 +1301,37 @@
         <v>46</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D10" s="6">
         <v>3</v>
       </c>
       <c r="E10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="6">
+        <v>3</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F11" s="6" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
@@ -1366,8 +1373,16 @@
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:F16" xr:uid="{D99DBC6D-CD22-4065-BC1A-0B9DFEE9E78B}"/>
+  <autoFilter ref="A3:F17" xr:uid="{D99DBC6D-CD22-4065-BC1A-0B9DFEE9E78B}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
